--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/76.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/76.xlsx
@@ -426,13 +426,13 @@
         <v>-3.845019480553937</v>
       </c>
       <c r="E2">
-        <v>-3.440804554845655</v>
+        <v>-11.34785527931467</v>
       </c>
       <c r="F2">
-        <v>-2.829513499075378</v>
+        <v>-3.023121185192484</v>
       </c>
       <c r="G2">
-        <v>-6.921949052466908</v>
+        <v>-11.41954897499181</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.929453411264621</v>
       </c>
       <c r="E3">
-        <v>-3.041710140549666</v>
+        <v>-12.47850655565377</v>
       </c>
       <c r="F3">
-        <v>-2.833122695849375</v>
+        <v>-2.560972526068432</v>
       </c>
       <c r="G3">
-        <v>-6.860114432179172</v>
+        <v>-10.82525412614519</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.285616450854774</v>
       </c>
       <c r="E4">
-        <v>-4.785553025319398</v>
+        <v>-13.9095586837657</v>
       </c>
       <c r="F4">
-        <v>-2.740883157180248</v>
+        <v>-3.039727466516406</v>
       </c>
       <c r="G4">
-        <v>-7.462602491259733</v>
+        <v>-11.01289406224359</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.062532423443395</v>
       </c>
       <c r="E5">
-        <v>-5.020100808072677</v>
+        <v>-13.5145942377647</v>
       </c>
       <c r="F5">
-        <v>-2.86915253603414</v>
+        <v>-2.748500823816392</v>
       </c>
       <c r="G5">
-        <v>-6.21119052558935</v>
+        <v>-10.14975232492386</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.182232500374325</v>
       </c>
       <c r="E6">
-        <v>-5.251261292268217</v>
+        <v>-13.71728420587402</v>
       </c>
       <c r="F6">
-        <v>-2.736935158138505</v>
+        <v>-2.738703722543482</v>
       </c>
       <c r="G6">
-        <v>-6.985296315893548</v>
+        <v>-9.925769578833048</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.580121358505468</v>
       </c>
       <c r="E7">
-        <v>-6.201941954594487</v>
+        <v>-15.96173177829568</v>
       </c>
       <c r="F7">
-        <v>-2.679180554447921</v>
+        <v>-2.950549573768025</v>
       </c>
       <c r="G7">
-        <v>-6.664786593966988</v>
+        <v>-8.962658864261716</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.143232267379571</v>
       </c>
       <c r="E8">
-        <v>-7.082517310808011</v>
+        <v>-15.23597589145639</v>
       </c>
       <c r="F8">
-        <v>-2.764702033480344</v>
+        <v>-2.904053311448889</v>
       </c>
       <c r="G8">
-        <v>-6.6656593989018</v>
+        <v>-9.979342083234101</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.76962457097666</v>
       </c>
       <c r="E9">
-        <v>-7.133032438363573</v>
+        <v>-15.13996318554576</v>
       </c>
       <c r="F9">
-        <v>-2.656098096768913</v>
+        <v>-2.710494499008548</v>
       </c>
       <c r="G9">
-        <v>-5.944745491297761</v>
+        <v>-10.14960138873213</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.35212472846934</v>
       </c>
       <c r="E10">
-        <v>-7.921747699331504</v>
+        <v>-16.46615849801008</v>
       </c>
       <c r="F10">
-        <v>-2.469775901959428</v>
+        <v>-2.561021399745196</v>
       </c>
       <c r="G10">
-        <v>-5.542654757738727</v>
+        <v>-9.308450398303798</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.806414477565471</v>
       </c>
       <c r="E11">
-        <v>-8.155534698451493</v>
+        <v>-16.15655125857966</v>
       </c>
       <c r="F11">
-        <v>-2.716613649013027</v>
+        <v>-2.489188692044034</v>
       </c>
       <c r="G11">
-        <v>-5.563743168701278</v>
+        <v>-9.150174113940864</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.064292240494268</v>
       </c>
       <c r="E12">
-        <v>-8.894554485659251</v>
+        <v>-17.24457600908457</v>
       </c>
       <c r="F12">
-        <v>-2.284777438259618</v>
+        <v>-2.392819741871951</v>
       </c>
       <c r="G12">
-        <v>-4.763978225802223</v>
+        <v>-9.115038793482329</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.087190190696551</v>
       </c>
       <c r="E13">
-        <v>-9.846503120707666</v>
+        <v>-17.96733857460479</v>
       </c>
       <c r="F13">
-        <v>-2.427636023811615</v>
+        <v>-2.437563178766764</v>
       </c>
       <c r="G13">
-        <v>-4.356342227807728</v>
+        <v>-8.650926410006671</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.868457034329539</v>
       </c>
       <c r="E14">
-        <v>-10.59588405644497</v>
+        <v>-19.4658060952689</v>
       </c>
       <c r="F14">
-        <v>-2.775759081572912</v>
+        <v>-2.297844105671377</v>
       </c>
       <c r="G14">
-        <v>-3.821686862025568</v>
+        <v>-7.704136491472018</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.433380300258987</v>
       </c>
       <c r="E15">
-        <v>-11.16819260153435</v>
+        <v>-20.29622407337347</v>
       </c>
       <c r="F15">
-        <v>-2.325779139595984</v>
+        <v>-2.409614890963711</v>
       </c>
       <c r="G15">
-        <v>-2.874545852784054</v>
+        <v>-7.62612216767466</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.836249797161289</v>
       </c>
       <c r="E16">
-        <v>-12.05466855937987</v>
+        <v>-19.69752811024139</v>
       </c>
       <c r="F16">
-        <v>-2.170237420739724</v>
+        <v>-1.96699582172806</v>
       </c>
       <c r="G16">
-        <v>-2.272166074014955</v>
+        <v>-6.180862194715402</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.153558750240933</v>
       </c>
       <c r="E17">
-        <v>-12.54349921461186</v>
+        <v>-19.98022262864422</v>
       </c>
       <c r="F17">
-        <v>-2.14473281677493</v>
+        <v>-1.554339629819069</v>
       </c>
       <c r="G17">
-        <v>-1.608411045976443</v>
+        <v>-6.481162873057342</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.471141573120494</v>
       </c>
       <c r="E18">
-        <v>-13.45126352876743</v>
+        <v>-21.61242504370286</v>
       </c>
       <c r="F18">
-        <v>-1.477178862983101</v>
+        <v>-1.67097376013324</v>
       </c>
       <c r="G18">
-        <v>-1.29264597042484</v>
+        <v>-7.016313703294978</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.872824268460892</v>
       </c>
       <c r="E19">
-        <v>-13.71601170467786</v>
+        <v>-21.66878190272832</v>
       </c>
       <c r="F19">
-        <v>-1.343054583326222</v>
+        <v>-1.270640361708295</v>
       </c>
       <c r="G19">
-        <v>-0.9257627441986481</v>
+        <v>-5.930678894472421</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.425514297962036</v>
       </c>
       <c r="E20">
-        <v>-15.00136923854101</v>
+        <v>-22.24524305848273</v>
       </c>
       <c r="F20">
-        <v>-0.9414686933882439</v>
+        <v>-1.342177342246657</v>
       </c>
       <c r="G20">
-        <v>-0.6916968042556593</v>
+        <v>-5.388827809810399</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.171014720512577</v>
       </c>
       <c r="E21">
-        <v>-16.12395077419845</v>
+        <v>-23.46376937294068</v>
       </c>
       <c r="F21">
-        <v>-0.6864690423148608</v>
+        <v>-0.5876754607547834</v>
       </c>
       <c r="G21">
-        <v>-0.4893012148044309</v>
+        <v>-5.342916957750649</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.122921197270129</v>
       </c>
       <c r="E22">
-        <v>-16.84351170859524</v>
+        <v>-24.17339030689064</v>
       </c>
       <c r="F22">
-        <v>-0.6130508394047407</v>
+        <v>-0.5926274410887189</v>
       </c>
       <c r="G22">
-        <v>-0.5162597311368287</v>
+        <v>-6.718441128907028</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.265651219520219</v>
       </c>
       <c r="E23">
-        <v>-17.504600986605</v>
+        <v>-24.69113074018759</v>
       </c>
       <c r="F23">
-        <v>-0.1945587991430276</v>
+        <v>-0.7581509871487133</v>
       </c>
       <c r="G23">
-        <v>-0.5712628481378005</v>
+        <v>-4.961740730411516</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.563156677658344</v>
       </c>
       <c r="E24">
-        <v>-17.31199593011076</v>
+        <v>-24.44424286576341</v>
       </c>
       <c r="F24">
-        <v>-0.2072435891820965</v>
+        <v>-0.4139784135313663</v>
       </c>
       <c r="G24">
-        <v>-1.296645779505803</v>
+        <v>-5.405128918517721</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.961756777533924</v>
       </c>
       <c r="E25">
-        <v>-17.76392405065424</v>
+        <v>-24.28879846697612</v>
       </c>
       <c r="F25">
-        <v>0.1983027253086659</v>
+        <v>-0.2258528628859874</v>
       </c>
       <c r="G25">
-        <v>-1.128519268021415</v>
+        <v>-5.830772260430448</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.398166384602645</v>
       </c>
       <c r="E26">
-        <v>-17.61368739697577</v>
+        <v>-25.32905234517411</v>
       </c>
       <c r="F26">
-        <v>-0.04173661047015804</v>
+        <v>-0.2346758040932049</v>
       </c>
       <c r="G26">
-        <v>-1.322508367837346</v>
+        <v>-5.687005537803379</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.80683860808306</v>
       </c>
       <c r="E27">
-        <v>-18.06361393200786</v>
+        <v>-25.54311783999069</v>
       </c>
       <c r="F27">
-        <v>0.1725578947970601</v>
+        <v>0.03943511133016551</v>
       </c>
       <c r="G27">
-        <v>-2.127572483554905</v>
+        <v>-7.456168015781661</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.127399468896623</v>
       </c>
       <c r="E28">
-        <v>-17.95030698386194</v>
+        <v>-26.70060032482524</v>
       </c>
       <c r="F28">
-        <v>0.08466231478821291</v>
+        <v>0.1004269748308903</v>
       </c>
       <c r="G28">
-        <v>-1.823997146096639</v>
+        <v>-6.212263485039289</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.314153331740597</v>
       </c>
       <c r="E29">
-        <v>-17.6517265786402</v>
+        <v>-25.11736882768555</v>
       </c>
       <c r="F29">
-        <v>0.210490494906055</v>
+        <v>0.07717967203872499</v>
       </c>
       <c r="G29">
-        <v>-2.176462684790631</v>
+        <v>-6.832598108181669</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.337770878146477</v>
       </c>
       <c r="E30">
-        <v>-16.99709943303939</v>
+        <v>-25.44312460542732</v>
       </c>
       <c r="F30">
-        <v>0.2200382575907221</v>
+        <v>-0.1442934651411536</v>
       </c>
       <c r="G30">
-        <v>-2.302202376170112</v>
+        <v>-6.604356336506695</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.186502457533026</v>
       </c>
       <c r="E31">
-        <v>-17.21179891421705</v>
+        <v>-25.4147718296653</v>
       </c>
       <c r="F31">
-        <v>0.06817780347250275</v>
+        <v>-0.121906836080497</v>
       </c>
       <c r="G31">
-        <v>-2.458270398423541</v>
+        <v>-5.713163436075272</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.866100007852267</v>
       </c>
       <c r="E32">
-        <v>-16.68340298158005</v>
+        <v>-25.29155205191659</v>
       </c>
       <c r="F32">
-        <v>0.1116513531388236</v>
+        <v>0.07697589365763631</v>
       </c>
       <c r="G32">
-        <v>-2.665814224501537</v>
+        <v>-6.354271472910496</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.398862668965693</v>
       </c>
       <c r="E33">
-        <v>-16.38951860390427</v>
+        <v>-24.78964769222446</v>
       </c>
       <c r="F33">
-        <v>0.07120962816674895</v>
+        <v>-0.04051394018362597</v>
       </c>
       <c r="G33">
-        <v>-3.446876204511758</v>
+        <v>-7.287024325613846</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.820084077373773</v>
       </c>
       <c r="E34">
-        <v>-16.81780809012771</v>
+        <v>-24.14835690257624</v>
       </c>
       <c r="F34">
-        <v>0.07696926671841391</v>
+        <v>0.7003057969162083</v>
       </c>
       <c r="G34">
-        <v>-2.931278173546853</v>
+        <v>-7.788582009525887</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.174213985732674</v>
       </c>
       <c r="E35">
-        <v>-16.19670070913167</v>
+        <v>-23.00542440472833</v>
       </c>
       <c r="F35">
-        <v>0.2697270478802477</v>
+        <v>-0.151691614415556</v>
       </c>
       <c r="G35">
-        <v>-2.886643716673726</v>
+        <v>-7.848221492590354</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.5103121289061927</v>
       </c>
       <c r="E36">
-        <v>-16.10690106955957</v>
+        <v>-24.1073606273848</v>
       </c>
       <c r="F36">
-        <v>0.2037252183273915</v>
+        <v>-0.1557348757086204</v>
       </c>
       <c r="G36">
-        <v>-2.414843431084289</v>
+        <v>-6.427134278859525</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.1227704951678857</v>
       </c>
       <c r="E37">
-        <v>-15.39124820823139</v>
+        <v>-23.88405704559256</v>
       </c>
       <c r="F37">
-        <v>0.3149351988880307</v>
+        <v>0.1825819687383369</v>
       </c>
       <c r="G37">
-        <v>-2.98252429186226</v>
+        <v>-6.894905224373964</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.6821036432432792</v>
       </c>
       <c r="E38">
-        <v>-15.9457417365746</v>
+        <v>-22.45072709505478</v>
       </c>
       <c r="F38">
-        <v>0.5006526854934714</v>
+        <v>-0.3586890312315133</v>
       </c>
       <c r="G38">
-        <v>-2.715160515534027</v>
+        <v>-7.579755225818147</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.133771932124507</v>
       </c>
       <c r="E39">
-        <v>-14.60353374001915</v>
+        <v>-21.49569909768115</v>
       </c>
       <c r="F39">
-        <v>0.4090178550283873</v>
+        <v>0.4011616185802368</v>
       </c>
       <c r="G39">
-        <v>-2.124097669923453</v>
+        <v>-6.503996893889518</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.455664258564502</v>
       </c>
       <c r="E40">
-        <v>-14.89595542059046</v>
+        <v>-22.17847976618765</v>
       </c>
       <c r="F40">
-        <v>0.4214847844405199</v>
+        <v>0.2772171459363608</v>
       </c>
       <c r="G40">
-        <v>-2.022245271496729</v>
+        <v>-7.329178178988032</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.63946914340687</v>
       </c>
       <c r="E41">
-        <v>-14.16526349708281</v>
+        <v>-20.87409358454427</v>
       </c>
       <c r="F41">
-        <v>0.4763359603842919</v>
+        <v>0.5461184587635252</v>
       </c>
       <c r="G41">
-        <v>-2.441601792901561</v>
+        <v>-6.417028116456436</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.691044074162561</v>
       </c>
       <c r="E42">
-        <v>-14.14219092201373</v>
+        <v>-21.21755569565603</v>
       </c>
       <c r="F42">
-        <v>0.4751356560176355</v>
+        <v>0.03480205244630788</v>
       </c>
       <c r="G42">
-        <v>-1.902720213750837</v>
+        <v>-7.251705256747983</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.628511395847655</v>
       </c>
       <c r="E43">
-        <v>-13.34055592470192</v>
+        <v>-20.95326036714636</v>
       </c>
       <c r="F43">
-        <v>0.346322039780104</v>
+        <v>0.01618780853800019</v>
       </c>
       <c r="G43">
-        <v>-1.908344227503725</v>
+        <v>-6.536412081675272</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.476662225248871</v>
       </c>
       <c r="E44">
-        <v>-12.58883376790264</v>
+        <v>-21.66794866351091</v>
       </c>
       <c r="F44">
-        <v>0.4115120692782167</v>
+        <v>-0.06279205311451588</v>
       </c>
       <c r="G44">
-        <v>-1.548663282600514</v>
+        <v>-6.449643458757317</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.26296519051718</v>
       </c>
       <c r="E45">
-        <v>-12.61418869387159</v>
+        <v>-20.8496715242209</v>
       </c>
       <c r="F45">
-        <v>0.3238558874487786</v>
+        <v>0.2851106589176373</v>
       </c>
       <c r="G45">
-        <v>-1.376218683543897</v>
+        <v>-6.234218138493533</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.01381631831049</v>
       </c>
       <c r="E46">
-        <v>-12.65955041800642</v>
+        <v>-20.45387836747651</v>
       </c>
       <c r="F46">
-        <v>0.3003567609661622</v>
+        <v>-0.3560216881944989</v>
       </c>
       <c r="G46">
-        <v>-1.301958077210544</v>
+        <v>-5.686608509994685</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.7514317023013977</v>
       </c>
       <c r="E47">
-        <v>-12.10125297149678</v>
+        <v>-18.8332643174035</v>
       </c>
       <c r="F47">
-        <v>0.4610674924158915</v>
+        <v>0.2554459938559842</v>
       </c>
       <c r="G47">
-        <v>-1.122432602028645</v>
+        <v>-6.55457036178524</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.4920599731790223</v>
       </c>
       <c r="E48">
-        <v>-11.00764914101442</v>
+        <v>-20.34518140587039</v>
       </c>
       <c r="F48">
-        <v>0.2224471499980631</v>
+        <v>-0.3629973700934735</v>
       </c>
       <c r="G48">
-        <v>-1.286598679090784</v>
+        <v>-6.410383642798561</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.2448576093058264</v>
       </c>
       <c r="E49">
-        <v>-11.20988173324897</v>
+        <v>-19.06257718420391</v>
       </c>
       <c r="F49">
-        <v>0.2851404801441381</v>
+        <v>0.07269489091996846</v>
       </c>
       <c r="G49">
-        <v>-1.075845818327649</v>
+        <v>-5.14933144818653</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.01168168581185385</v>
       </c>
       <c r="E50">
-        <v>-10.58590782820608</v>
+        <v>-18.88548667965995</v>
       </c>
       <c r="F50">
-        <v>0.303708335477889</v>
+        <v>-0.2991045639481448</v>
       </c>
       <c r="G50">
-        <v>-1.192909959903959</v>
+        <v>-7.057834280908192</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.2114964526630657</v>
       </c>
       <c r="E51">
-        <v>-10.30937656292769</v>
+        <v>-18.63296538357023</v>
       </c>
       <c r="F51">
-        <v>0.4616680587829211</v>
+        <v>0.2008946869120256</v>
       </c>
       <c r="G51">
-        <v>-1.041891737630515</v>
+        <v>-5.599656138669401</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.4331863611152268</v>
       </c>
       <c r="E52">
-        <v>-9.554914679353772</v>
+        <v>-18.20617482224333</v>
       </c>
       <c r="F52">
-        <v>0.3768548338798909</v>
+        <v>0.03450715365091125</v>
       </c>
       <c r="G52">
-        <v>-0.6921069569505899</v>
+        <v>-6.106329246992616</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.6635332035741506</v>
       </c>
       <c r="E53">
-        <v>-9.061990283618854</v>
+        <v>-18.02611363875034</v>
       </c>
       <c r="F53">
-        <v>0.1105322287776415</v>
+        <v>0.04610098382049314</v>
       </c>
       <c r="G53">
-        <v>-1.032605880617287</v>
+        <v>-6.648912044062394</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.9118229397010612</v>
       </c>
       <c r="E54">
-        <v>-8.68654356059092</v>
+        <v>-17.7608899730691</v>
       </c>
       <c r="F54">
-        <v>0.4491713081442878</v>
+        <v>0.215242010328513</v>
       </c>
       <c r="G54">
-        <v>-1.58958011544679</v>
+        <v>-5.82237233323827</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.184607758260466</v>
       </c>
       <c r="E55">
-        <v>-9.058317691198633</v>
+        <v>-15.53812926267018</v>
       </c>
       <c r="F55">
-        <v>0.4985635429036111</v>
+        <v>-0.4650439504443446</v>
       </c>
       <c r="G55">
-        <v>-1.481309647649792</v>
+        <v>-6.150816048895567</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.483184029917922</v>
       </c>
       <c r="E56">
-        <v>-7.943633814210575</v>
+        <v>-15.65523560050853</v>
       </c>
       <c r="F56">
-        <v>0.408944958696941</v>
+        <v>0.3684585018851151</v>
       </c>
       <c r="G56">
-        <v>-1.780399555236297</v>
+        <v>-5.444736543961778</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.803023532057048</v>
       </c>
       <c r="E57">
-        <v>-7.867759232212058</v>
+        <v>-15.73778515319436</v>
       </c>
       <c r="F57">
-        <v>0.5554019722466992</v>
+        <v>0.004791958177687388</v>
       </c>
       <c r="G57">
-        <v>-2.320787215082807</v>
+        <v>-5.752206691411105</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.134080163417201</v>
       </c>
       <c r="E58">
-        <v>-6.488893238564526</v>
+        <v>-14.57116873628634</v>
       </c>
       <c r="F58">
-        <v>0.6059009058561626</v>
+        <v>-0.2763667071087012</v>
       </c>
       <c r="G58">
-        <v>-2.56824382020989</v>
+        <v>-6.457606983482089</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.465510046338278</v>
       </c>
       <c r="E59">
-        <v>-7.293689110733695</v>
+        <v>-15.33110554493552</v>
       </c>
       <c r="F59">
-        <v>0.506488533846194</v>
+        <v>0.2832219812392544</v>
       </c>
       <c r="G59">
-        <v>-2.290232479921257</v>
+        <v>-7.627946526861711</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.789457569704976</v>
       </c>
       <c r="E60">
-        <v>-7.136542005719518</v>
+        <v>-15.27403771549086</v>
       </c>
       <c r="F60">
-        <v>0.6500735976104463</v>
+        <v>0.366071147030247</v>
       </c>
       <c r="G60">
-        <v>-2.897068157568082</v>
+        <v>-7.78560594157147</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.099995220455102</v>
       </c>
       <c r="E61">
-        <v>-5.969336887190498</v>
+        <v>-14.47388805765356</v>
       </c>
       <c r="F61">
-        <v>0.6193113457400838</v>
+        <v>0.6469763318913789</v>
       </c>
       <c r="G61">
-        <v>-2.550567879669161</v>
+        <v>-7.206319400137743</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.393185196453858</v>
       </c>
       <c r="E62">
-        <v>-6.708940847545244</v>
+        <v>-13.83915449836844</v>
       </c>
       <c r="F62">
-        <v>0.6742925753660954</v>
+        <v>-0.02647476944097995</v>
       </c>
       <c r="G62">
-        <v>-3.521166341839145</v>
+        <v>-7.237618972593286</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.666725303866478</v>
       </c>
       <c r="E63">
-        <v>-5.464117684524755</v>
+        <v>-14.49370013143712</v>
       </c>
       <c r="F63">
-        <v>0.7270305860653259</v>
+        <v>0.1624079090105577</v>
       </c>
       <c r="G63">
-        <v>-3.575874148899767</v>
+        <v>-7.926206285393676</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.919990396327123</v>
       </c>
       <c r="E64">
-        <v>-5.632282566799594</v>
+        <v>-13.95611139656455</v>
       </c>
       <c r="F64">
-        <v>0.6129677081694452</v>
+        <v>0.2240442423506605</v>
       </c>
       <c r="G64">
-        <v>-3.83715782167835</v>
+        <v>-8.375832075684386</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.153931976947981</v>
       </c>
       <c r="E65">
-        <v>-6.45099896806834</v>
+        <v>-15.02597243782468</v>
       </c>
       <c r="F65">
-        <v>0.7670970606039325</v>
+        <v>0.01757366720288376</v>
       </c>
       <c r="G65">
-        <v>-3.537227921372627</v>
+        <v>-9.260406752230407</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.369364371080919</v>
       </c>
       <c r="E66">
-        <v>-4.80514320387658</v>
+        <v>-14.39166002662228</v>
       </c>
       <c r="F66">
-        <v>0.1858507065097837</v>
+        <v>0.4868802490545269</v>
       </c>
       <c r="G66">
-        <v>-3.826913847969764</v>
+        <v>-7.961837070307687</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.569062532981929</v>
       </c>
       <c r="E67">
-        <v>-4.956942181087698</v>
+        <v>-13.61623130839286</v>
       </c>
       <c r="F67">
-        <v>0.4826356944825822</v>
+        <v>0.1455315799133234</v>
       </c>
       <c r="G67">
-        <v>-3.871220182686946</v>
+        <v>-9.114956762943343</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.756810903938804</v>
       </c>
       <c r="E68">
-        <v>-5.282154541948545</v>
+        <v>-13.59374743494477</v>
       </c>
       <c r="F68">
-        <v>0.456805542128488</v>
+        <v>0.1410236045072885</v>
       </c>
       <c r="G68">
-        <v>-3.838959212314485</v>
+        <v>-8.950229596994539</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.936082590298291</v>
       </c>
       <c r="E69">
-        <v>-4.70791233845789</v>
+        <v>-13.77744045459191</v>
       </c>
       <c r="F69">
-        <v>0.3997434535866441</v>
+        <v>-0.0508610774119946</v>
       </c>
       <c r="G69">
-        <v>-4.583491352703407</v>
+        <v>-9.005272088654225</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.111827830702989</v>
       </c>
       <c r="E70">
-        <v>-5.575943821670167</v>
+        <v>-13.10120795950051</v>
       </c>
       <c r="F70">
-        <v>0.2812579221272168</v>
+        <v>-0.603063213629187</v>
       </c>
       <c r="G70">
-        <v>-4.337855825541816</v>
+        <v>-9.006154737253716</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.286317378650218</v>
       </c>
       <c r="E71">
-        <v>-5.29958010993006</v>
+        <v>-13.05708703724377</v>
       </c>
       <c r="F71">
-        <v>0.5236431943907689</v>
+        <v>-0.1176216915058152</v>
       </c>
       <c r="G71">
-        <v>-4.226048200903738</v>
+        <v>-8.440711669579287</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.462049222902338</v>
       </c>
       <c r="E72">
-        <v>-5.400094119004311</v>
+        <v>-13.31733390999058</v>
       </c>
       <c r="F72">
-        <v>0.1619365679583648</v>
+        <v>0.3954127488048083</v>
       </c>
       <c r="G72">
-        <v>-4.414554379493836</v>
+        <v>-9.303817313461861</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.642680900366228</v>
       </c>
       <c r="E73">
-        <v>-5.575500031217415</v>
+        <v>-14.36563941497421</v>
       </c>
       <c r="F73">
-        <v>0.1468288032661074</v>
+        <v>-0.1712642794089027</v>
       </c>
       <c r="G73">
-        <v>-3.876427481301784</v>
+        <v>-9.860899828602827</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.833096767447675</v>
       </c>
       <c r="E74">
-        <v>-5.668206951102443</v>
+        <v>-13.81050284332191</v>
       </c>
       <c r="F74">
-        <v>0.07290281113807114</v>
+        <v>-0.2102754138763427</v>
       </c>
       <c r="G74">
-        <v>-4.18283779418741</v>
+        <v>-8.801429480495282</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.042675389223282</v>
       </c>
       <c r="E75">
-        <v>-6.160071683919567</v>
+        <v>-13.1101788665097</v>
       </c>
       <c r="F75">
-        <v>-0.07451925043594848</v>
+        <v>-0.5586411832866608</v>
       </c>
       <c r="G75">
-        <v>-4.316170232255446</v>
+        <v>-8.937422989248027</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.276542236650817</v>
       </c>
       <c r="E76">
-        <v>-6.338701869626131</v>
+        <v>-14.15671826663034</v>
       </c>
       <c r="F76">
-        <v>-0.2102505628542587</v>
+        <v>-0.5690065445978909</v>
       </c>
       <c r="G76">
-        <v>-4.080778678802441</v>
+        <v>-9.548944251281739</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.534055308213389</v>
       </c>
       <c r="E77">
-        <v>-6.85277423897687</v>
+        <v>-13.87433621293404</v>
       </c>
       <c r="F77">
-        <v>-0.06582139270655367</v>
+        <v>-0.2132724471396713</v>
       </c>
       <c r="G77">
-        <v>-4.066613645330319</v>
+        <v>-8.582434191174823</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.807625962538773</v>
       </c>
       <c r="E78">
-        <v>-6.903307480428464</v>
+        <v>-16.17052160089333</v>
       </c>
       <c r="F78">
-        <v>-0.1546091244082159</v>
+        <v>-0.7550056761202836</v>
       </c>
       <c r="G78">
-        <v>-4.024279324770363</v>
+        <v>-9.304614650300808</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.084713940029292</v>
       </c>
       <c r="E79">
-        <v>-7.513415198059868</v>
+        <v>-15.65934292643349</v>
       </c>
       <c r="F79">
-        <v>-0.3129316726356742</v>
+        <v>-0.8985923966193414</v>
       </c>
       <c r="G79">
-        <v>-3.838867338110821</v>
+        <v>-8.452783283696483</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.35365906531936</v>
       </c>
       <c r="E80">
-        <v>-8.203975784911544</v>
+        <v>-16.79923228974824</v>
       </c>
       <c r="F80">
-        <v>-0.3646756424515453</v>
+        <v>-0.6402163200121477</v>
       </c>
       <c r="G80">
-        <v>-3.238535041594815</v>
+        <v>-7.988756211981371</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.598919886285944</v>
       </c>
       <c r="E81">
-        <v>-8.616420140582145</v>
+        <v>-15.8195784507209</v>
       </c>
       <c r="F81">
-        <v>-0.1450920113174524</v>
+        <v>-0.7927444382570235</v>
       </c>
       <c r="G81">
-        <v>-3.497551390275822</v>
+        <v>-7.791134799899135</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.805733290867631</v>
       </c>
       <c r="E82">
-        <v>-9.493019496616935</v>
+        <v>-17.13544431397372</v>
       </c>
       <c r="F82">
-        <v>-0.3346746602243556</v>
+        <v>-1.120424216884632</v>
       </c>
       <c r="G82">
-        <v>-3.171689995985808</v>
+        <v>-8.161095811948085</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.961227418109076</v>
       </c>
       <c r="E83">
-        <v>-10.01460007587239</v>
+        <v>-18.85414963952687</v>
       </c>
       <c r="F83">
-        <v>-0.3865006384131039</v>
+        <v>-0.8854992214506925</v>
       </c>
       <c r="G83">
-        <v>-3.252198048168343</v>
+        <v>-7.601581911631573</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.056037833351509</v>
       </c>
       <c r="E84">
-        <v>-11.42211772456645</v>
+        <v>-17.95726271993772</v>
       </c>
       <c r="F84">
-        <v>-0.5075640492300433</v>
+        <v>-0.8075183708859526</v>
       </c>
       <c r="G84">
-        <v>-2.657913042986395</v>
+        <v>-8.242207608897559</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.091688542080442</v>
       </c>
       <c r="E85">
-        <v>-12.68031347133159</v>
+        <v>-19.06058012716653</v>
       </c>
       <c r="F85">
-        <v>-0.7196443284295783</v>
+        <v>-0.993927544272731</v>
       </c>
       <c r="G85">
-        <v>-3.529628612240953</v>
+        <v>-7.667209624042027</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.074290986028977</v>
       </c>
       <c r="E86">
-        <v>-13.52706565518183</v>
+        <v>-20.97609293309304</v>
       </c>
       <c r="F86">
-        <v>-0.8019285476518615</v>
+        <v>-1.420550838960324</v>
       </c>
       <c r="G86">
-        <v>-2.75963419255074</v>
+        <v>-8.013867400575801</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.015959975843424</v>
       </c>
       <c r="E87">
-        <v>-14.19801342110628</v>
+        <v>-22.55727303150725</v>
       </c>
       <c r="F87">
-        <v>-0.93187454212902</v>
+        <v>-1.147865543837171</v>
       </c>
       <c r="G87">
-        <v>-2.48303049631111</v>
+        <v>-6.082376329608669</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.932050028856495</v>
       </c>
       <c r="E88">
-        <v>-16.49384105961897</v>
+        <v>-22.19787069188849</v>
       </c>
       <c r="F88">
-        <v>-0.9998677669182062</v>
+        <v>-1.067738393331778</v>
       </c>
       <c r="G88">
-        <v>-2.538529077767558</v>
+        <v>-6.982914149041391</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.837512895695739</v>
       </c>
       <c r="E89">
-        <v>-17.78805628864112</v>
+        <v>-24.60202848561267</v>
       </c>
       <c r="F89">
-        <v>-1.500310194338874</v>
+        <v>-1.333843966174494</v>
       </c>
       <c r="G89">
-        <v>-2.272212011116787</v>
+        <v>-7.247666073008307</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.754036817547892</v>
       </c>
       <c r="E90">
-        <v>-19.33811218520061</v>
+        <v>-26.39270937704373</v>
       </c>
       <c r="F90">
-        <v>-1.361798880916769</v>
+        <v>-1.737832949947993</v>
       </c>
       <c r="G90">
-        <v>-2.411972362219776</v>
+        <v>-6.605176641896556</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.699885759170472</v>
       </c>
       <c r="E91">
-        <v>-20.74950620764524</v>
+        <v>-27.15259184400483</v>
       </c>
       <c r="F91">
-        <v>-1.442326961245117</v>
+        <v>-1.553120273002148</v>
       </c>
       <c r="G91">
-        <v>-2.458972579837261</v>
+        <v>-6.914743489922367</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.690277221395045</v>
       </c>
       <c r="E92">
-        <v>-24.05395633341234</v>
+        <v>-29.03136514030711</v>
       </c>
       <c r="F92">
-        <v>-1.463758482690346</v>
+        <v>-1.755589833594404</v>
       </c>
       <c r="G92">
-        <v>-2.015134864377413</v>
+        <v>-7.221901921323546</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.735376668173891</v>
       </c>
       <c r="E93">
-        <v>-25.40267627559081</v>
+        <v>-30.68700014411843</v>
       </c>
       <c r="F93">
-        <v>-1.769276119823457</v>
+        <v>-1.833571512526546</v>
       </c>
       <c r="G93">
-        <v>-2.187559776104673</v>
+        <v>-7.404308309034637</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.839503777657666</v>
       </c>
       <c r="E94">
-        <v>-27.63308557858869</v>
+        <v>-33.10534111843463</v>
       </c>
       <c r="F94">
-        <v>-1.741073523227745</v>
+        <v>-2.19489046301444</v>
       </c>
       <c r="G94">
-        <v>-2.066889572034534</v>
+        <v>-7.417534913140759</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.01001223388811</v>
       </c>
       <c r="E95">
-        <v>-30.0465901426647</v>
+        <v>-34.31223604740388</v>
       </c>
       <c r="F95">
-        <v>-1.771659332841311</v>
+        <v>-1.840382349312364</v>
       </c>
       <c r="G95">
-        <v>-1.985098562222256</v>
+        <v>-7.187180034781503</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.252769186333065</v>
       </c>
       <c r="E96">
-        <v>-32.28613337773605</v>
+        <v>-36.56831274107724</v>
       </c>
       <c r="F96">
-        <v>-1.911457929207367</v>
+        <v>-2.26217460530683</v>
       </c>
       <c r="G96">
-        <v>-2.521410944891935</v>
+        <v>-6.646090193521272</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.559855606230141</v>
       </c>
       <c r="E97">
-        <v>-34.95556012188155</v>
+        <v>-40.54532503375252</v>
       </c>
       <c r="F97">
-        <v>-2.162372072250143</v>
+        <v>-2.49436267484192</v>
       </c>
       <c r="G97">
-        <v>-2.46075428314404</v>
+        <v>-7.716828256463949</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.93740347053396</v>
       </c>
       <c r="E98">
-        <v>-37.65098936377908</v>
+        <v>-42.73210022544949</v>
       </c>
       <c r="F98">
-        <v>-2.189468798363118</v>
+        <v>-2.699816843186462</v>
       </c>
       <c r="G98">
-        <v>-3.130612383283119</v>
+        <v>-7.778879437374608</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.355651742175855</v>
       </c>
       <c r="E99">
-        <v>-40.27836016981534</v>
+        <v>-43.25550577973004</v>
       </c>
       <c r="F99">
-        <v>-2.456998334771246</v>
+        <v>-2.790091494376149</v>
       </c>
       <c r="G99">
-        <v>-3.166272699191164</v>
+        <v>-7.581057870777246</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.836234633475115</v>
       </c>
       <c r="E100">
-        <v>-42.84985413507095</v>
+        <v>-46.83130659651076</v>
       </c>
       <c r="F100">
-        <v>-2.802230390296773</v>
+        <v>-2.956575118255989</v>
       </c>
       <c r="G100">
-        <v>-3.518449490387925</v>
+        <v>-7.897282317347171</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.32529724150642</v>
       </c>
       <c r="E101">
-        <v>-44.84248685334808</v>
+        <v>-48.17744078003085</v>
       </c>
       <c r="F101">
-        <v>-2.664150656291527</v>
+        <v>-2.92639106683278</v>
       </c>
       <c r="G101">
-        <v>-3.82675963055647</v>
+        <v>-8.419058888508511</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.89061016333358</v>
       </c>
       <c r="E102">
-        <v>-48.3274306318759</v>
+        <v>-51.56742245861782</v>
       </c>
       <c r="F102">
-        <v>-2.799581271342621</v>
+        <v>-3.019032363692265</v>
       </c>
       <c r="G102">
-        <v>-3.956735378969194</v>
+        <v>-8.660058049606606</v>
       </c>
     </row>
   </sheetData>
